--- a/Bloque_1_Financial_Scoring_Generic_V4.xlsx
+++ b/Bloque_1_Financial_Scoring_Generic_V4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/177369afe0b533fe/Escritorio/IA OS/Dashboard/streamlit-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7A6B52F-38C9-4025-BAB6-84BD129FEE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{B7A6B52F-38C9-4025-BAB6-84BD129FEE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C37EC64-50F1-4345-8A35-1C42E2E1A4D3}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="19543" windowHeight="12377" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
